--- a/BA/Part 1_Stakeholder Analysis amp Management-20260912/Done/Manual/Artifacts/4. Communication Plan_VNS.xlsx
+++ b/BA/Part 1_Stakeholder Analysis amp Management-20260912/Done/Manual/Artifacts/4. Communication Plan_VNS.xlsx
@@ -203,7 +203,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -239,6 +239,21 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Звичайний" xfId="0" builtinId="0"/>
@@ -591,7 +606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:JZ14"/>
+  <dimension ref="A2:JZ31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="8.875" customWidth="1" style="1" min="1" max="1"/>
@@ -930,36 +945,36 @@
       <c r="JY4" s="6" t="n"/>
       <c r="JZ4" s="6" t="n"/>
     </row>
-    <row r="5" ht="18" customFormat="1" customHeight="1" s="3">
+    <row r="5" ht="28" customFormat="1" customHeight="1" s="3">
       <c r="A5" s="7" t="n"/>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="19" t="inlineStr">
         <is>
           <t>Team Standup</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
-        <is>
-          <t>Online call</t>
-        </is>
-      </c>
-      <c r="D5" s="9" t="inlineStr">
-        <is>
-          <t>Daily, 10:00</t>
-        </is>
-      </c>
-      <c r="E5" s="9" t="inlineStr">
-        <is>
-          <t>Share progress since yesterday, raise blockers, re-plan the day</t>
-        </is>
-      </c>
-      <c r="F5" s="9" t="inlineStr">
-        <is>
-          <t>Project Manager</t>
-        </is>
-      </c>
-      <c r="G5" s="9" t="inlineStr">
-        <is>
-          <t>Whole project team</t>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>Meeting (online)</t>
+        </is>
+      </c>
+      <c r="D5" s="19" t="inlineStr">
+        <is>
+          <t>Daily, 10:00, 15 min</t>
+        </is>
+      </c>
+      <c r="E5" s="21" t="inlineStr">
+        <is>
+          <t>Synchronise progress since the previous day, raise blockers and redistribute work within the team</t>
+        </is>
+      </c>
+      <c r="F5" s="19" t="inlineStr">
+        <is>
+          <t>Project Manager (N. Zankovych)</t>
+        </is>
+      </c>
+      <c r="G5" s="21" t="inlineStr">
+        <is>
+          <t>Whole project team: PO, PM, BA, Tech Lead, DevOps, QA</t>
         </is>
       </c>
       <c r="H5" s="1" t="n"/>
@@ -1242,300 +1257,300 @@
       <c r="JY5" s="1" t="n"/>
       <c r="JZ5" s="1" t="n"/>
     </row>
-    <row r="6" customFormat="1" s="1">
+    <row r="6" ht="42" customFormat="1" customHeight="1" s="1">
       <c r="A6" s="7" t="n"/>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>Weekly Planning</t>
-        </is>
-      </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="B6" s="19" t="inlineStr">
+        <is>
+          <t>Weekly Planning and Backlog Review</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t>Meeting</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
-        <is>
-          <t>Every Monday</t>
-        </is>
-      </c>
-      <c r="E6" s="9" t="inlineStr">
-        <is>
-          <t>Agree the weekly scope and the MVP backlog priorities</t>
-        </is>
-      </c>
-      <c r="F6" s="9" t="inlineStr">
-        <is>
-          <t>Product Owner</t>
-        </is>
-      </c>
-      <c r="G6" s="9" t="inlineStr">
+      <c r="D6" s="19" t="inlineStr">
+        <is>
+          <t>Weekly, Monday</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>Agree the scope of work for the week and the MVP backlog priorities; confirm the definition of ready</t>
+        </is>
+      </c>
+      <c r="F6" s="19" t="inlineStr">
+        <is>
+          <t>Product Owner (K. Holovskyi)</t>
+        </is>
+      </c>
+      <c r="G6" s="21" t="inlineStr">
         <is>
           <t>PO, PM, BA, Tech Lead, DevOps, QA</t>
         </is>
       </c>
     </row>
-    <row r="7" customFormat="1" s="1">
+    <row r="7" ht="42" customFormat="1" customHeight="1" s="1">
       <c r="A7" s="7" t="n"/>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>Elicitation meeting</t>
-        </is>
-      </c>
-      <c r="C7" s="10" t="inlineStr">
-        <is>
-          <t>Interview</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>Every Thursday</t>
-        </is>
-      </c>
-      <c r="E7" s="9" t="inlineStr">
-        <is>
-          <t>Clarify lecturer scenarios: materials, assignments, analytics, AI</t>
-        </is>
-      </c>
-      <c r="F7" s="8" t="inlineStr">
-        <is>
-          <t>Business Analyst</t>
-        </is>
-      </c>
-      <c r="G7" s="14" t="inlineStr">
-        <is>
-          <t>N. Boiko, BA, PO and Tech Lead (optional)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" customFormat="1" s="1">
+      <c r="B7" s="19" t="inlineStr">
+        <is>
+          <t>Requirements Elicitation Meeting with Lecturers</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>Interview / workshop</t>
+        </is>
+      </c>
+      <c r="D7" s="19" t="inlineStr">
+        <is>
+          <t>Weekly, Thursday</t>
+        </is>
+      </c>
+      <c r="E7" s="21" t="inlineStr">
+        <is>
+          <t>Clarify lecturer scenarios: materials, assignments, activity analytics, AI mode for graded work</t>
+        </is>
+      </c>
+      <c r="F7" s="19" t="inlineStr">
+        <is>
+          <t>Business Analyst (A. Lysun)</t>
+        </is>
+      </c>
+      <c r="G7" s="21" t="inlineStr">
+        <is>
+          <t>End users — lecturers, BA; PO and Tech Lead as needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="28" customFormat="1" customHeight="1" s="1">
       <c r="A8" s="7" t="n"/>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="19" t="inlineStr">
+        <is>
+          <t>End-user Feedback Session</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>Survey + usability test</t>
+        </is>
+      </c>
+      <c r="D8" s="19" t="inlineStr">
+        <is>
+          <t>Weekly during the pilot</t>
+        </is>
+      </c>
+      <c r="E8" s="21" t="inlineStr">
+        <is>
+          <t>Validate prototypes with students and lecturers and collect pain points on deadlines, grade forecast and communication</t>
+        </is>
+      </c>
+      <c r="F8" s="19" t="inlineStr">
+        <is>
+          <t>Business Analyst (A. Lysun)</t>
+        </is>
+      </c>
+      <c r="G8" s="21" t="inlineStr">
+        <is>
+          <t>End users — students and lecturers, BA, QA, PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="28" customFormat="1" customHeight="1" s="1">
+      <c r="A9" s="7" t="n"/>
+      <c r="B9" s="19" t="inlineStr">
         <is>
           <t>Technical Sync</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>Meeting + code review</t>
+        </is>
+      </c>
+      <c r="D9" s="19" t="inlineStr">
+        <is>
+          <t>Weekly, Tuesday</t>
+        </is>
+      </c>
+      <c r="E9" s="21" t="inlineStr">
+        <is>
+          <t>Discuss the custom backend architecture, the data model, deployment, technical debt and dependencies between modules</t>
+        </is>
+      </c>
+      <c r="F9" s="19" t="inlineStr">
+        <is>
+          <t>Tech Lead (D. Lunhul)</t>
+        </is>
+      </c>
+      <c r="G9" s="21" t="inlineStr">
+        <is>
+          <t>Software engineers (Tech Lead, DevOps, QA), PM; BA as needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="28" customFormat="1" customHeight="1" s="1">
+      <c r="A10" s="7" t="n"/>
+      <c r="B10" s="19" t="inlineStr">
+        <is>
+          <t>Quality and Defect Report</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>Written report + dashboard</t>
+        </is>
+      </c>
+      <c r="D10" s="19" t="inlineStr">
+        <is>
+          <t>Weekly, Friday</t>
+        </is>
+      </c>
+      <c r="E10" s="21" t="inlineStr">
+        <is>
+          <t>Report the state of the acceptance criteria, open defects and release risks, including grade forecast correctness</t>
+        </is>
+      </c>
+      <c r="F10" s="19" t="inlineStr">
+        <is>
+          <t>QA Specialist (V. Kamelchuk)</t>
+        </is>
+      </c>
+      <c r="G10" s="21" t="inlineStr">
+        <is>
+          <t>QA, PM, PO, Tech Lead</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="42" customFormat="1" customHeight="1" s="1">
+      <c r="A11" s="7" t="n"/>
+      <c r="B11" s="19" t="inlineStr">
+        <is>
+          <t>Requests to the University Technical Department</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>E-mail / ticket</t>
+        </is>
+      </c>
+      <c r="D11" s="19" t="inlineStr">
+        <is>
+          <t>As needed (registry export, infrastructure access)</t>
+        </is>
+      </c>
+      <c r="E11" s="21" t="inlineStr">
+        <is>
+          <t>Request the export of the student registry and access to university infrastructure, domain and certificates</t>
+        </is>
+      </c>
+      <c r="F11" s="19" t="inlineStr">
+        <is>
+          <t>DevOps (Y. Shevchuk)</t>
+        </is>
+      </c>
+      <c r="G11" s="21" t="inlineStr">
+        <is>
+          <t>Technical Department of Lviv Polytechnic, DevOps, Tech Lead</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="28" customFormat="1" customHeight="1" s="1">
+      <c r="A12" s="7" t="n"/>
+      <c r="B12" s="19" t="inlineStr">
+        <is>
+          <t>Status Report to the Sponsor</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>Meeting + written report</t>
+        </is>
+      </c>
+      <c r="D12" s="19" t="inlineStr">
+        <is>
+          <t>Every two weeks, Tuesday</t>
+        </is>
+      </c>
+      <c r="E12" s="21" t="inlineStr">
+        <is>
+          <t>Present progress, risks and decisions requiring escalation; confirm the scope for the next period</t>
+        </is>
+      </c>
+      <c r="F12" s="19" t="inlineStr">
+        <is>
+          <t>Project Manager (N. Zankovych)</t>
+        </is>
+      </c>
+      <c r="G12" s="21" t="inlineStr">
+        <is>
+          <t>Lviv Polytechnic National University, PM, PO, BA</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="42" customFormat="1" customHeight="1" s="1">
+      <c r="A13" s="7" t="n"/>
+      <c r="B13" s="19" t="inlineStr">
+        <is>
+          <t>Increment Demo for the Sponsor and End Users</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>Demo + working meeting</t>
+        </is>
+      </c>
+      <c r="D13" s="19" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="E13" s="21" t="inlineStr">
+        <is>
+          <t>Show the working increment, confirm that it matches the requirements and collect corrections</t>
+        </is>
+      </c>
+      <c r="F13" s="19" t="inlineStr">
+        <is>
+          <t>Product Owner (K. Holovskyi)</t>
+        </is>
+      </c>
+      <c r="G13" s="21" t="inlineStr">
+        <is>
+          <t>Lviv Polytechnic National University, end-user representatives, PO, PM, BA, QA</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="28" customFormat="1" customHeight="1" s="2">
+      <c r="A14" s="7" t="n"/>
+      <c r="B14" s="19" t="inlineStr">
+        <is>
+          <t>Team Retrospective</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
         <is>
           <t>Meeting</t>
         </is>
       </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>Every Tuesday</t>
-        </is>
-      </c>
-      <c r="E8" s="9" t="inlineStr">
-        <is>
-          <t>Discuss backend architecture, data model and technical debt</t>
-        </is>
-      </c>
-      <c r="F8" s="13" t="inlineStr">
-        <is>
-          <t>Tech Lead</t>
-        </is>
-      </c>
-      <c r="G8" s="12" t="inlineStr">
-        <is>
-          <t>Tech Lead, DevOps, QA, PM, BA (optional)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" customFormat="1" s="1">
-      <c r="A9" s="7" t="n"/>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>Quality Report</t>
-        </is>
-      </c>
-      <c r="C9" s="10" t="inlineStr">
-        <is>
-          <t>Report</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>Every Friday</t>
-        </is>
-      </c>
-      <c r="E9" s="9" t="inlineStr">
-        <is>
-          <t>Share acceptance criteria status, open defects and release risks</t>
-        </is>
-      </c>
-      <c r="F9" s="8" t="inlineStr">
-        <is>
-          <t>QA Specialist</t>
-        </is>
-      </c>
-      <c r="G9" s="15" t="inlineStr">
-        <is>
-          <t>QA, PM, PO, Tech Lead</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" customFormat="1" s="1">
-      <c r="A10" s="7" t="n"/>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>Tech Dept Sync</t>
-        </is>
-      </c>
-      <c r="C10" s="10" t="inlineStr">
-        <is>
-          <t>Meeting</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>Bi-weekly</t>
-        </is>
-      </c>
-      <c r="E10" s="9" t="inlineStr">
-        <is>
-          <t>Agree access to the student registry, infrastructure and security</t>
-        </is>
-      </c>
-      <c r="F10" s="8" t="inlineStr">
-        <is>
-          <t>DevOps</t>
-        </is>
-      </c>
-      <c r="G10" s="9" t="inlineStr">
-        <is>
-          <t>Technical Department, DevOps, Tech Lead, PM</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" customFormat="1" s="1">
-      <c r="A11" s="7" t="n"/>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>Sponsor Report</t>
-        </is>
-      </c>
-      <c r="C11" s="10" t="inlineStr">
-        <is>
-          <t>Meeting</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t>Bi-weekly, Tuesday</t>
-        </is>
-      </c>
-      <c r="E11" s="9" t="inlineStr">
-        <is>
-          <t>Present progress, risks and decisions that need escalation</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="inlineStr">
-        <is>
-          <t>Project Manager</t>
-        </is>
-      </c>
-      <c r="G11" s="9" t="inlineStr">
-        <is>
-          <t>Lviv Polytechnic, N. Boiko, PM, PO, BA</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" customFormat="1" s="1">
-      <c r="A12" s="7" t="n"/>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>Increment Demo</t>
-        </is>
-      </c>
-      <c r="C12" s="10" t="inlineStr">
-        <is>
-          <t>Demo</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>Once a month</t>
-        </is>
-      </c>
-      <c r="E12" s="9" t="inlineStr">
-        <is>
-          <t>Show the working increment and collect corrections</t>
-        </is>
-      </c>
-      <c r="F12" s="8" t="inlineStr">
-        <is>
-          <t>Product Owner</t>
-        </is>
-      </c>
-      <c r="G12" s="9" t="inlineStr">
-        <is>
-          <t>N. Boiko, PO, PM, BA, QA</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" customFormat="1" s="1">
-      <c r="A13" s="7" t="n"/>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>Student Feedback</t>
-        </is>
-      </c>
-      <c r="C13" s="10" t="inlineStr">
-        <is>
-          <t>Survey</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t>Weekly during pilot</t>
-        </is>
-      </c>
-      <c r="E13" s="9" t="inlineStr">
-        <is>
-          <t>Validate prototypes and collect student pain points</t>
-        </is>
-      </c>
-      <c r="F13" s="8" t="inlineStr">
-        <is>
-          <t>Business Analyst</t>
-        </is>
-      </c>
-      <c r="G13" s="9" t="inlineStr">
-        <is>
-          <t>Students, BA, QA, PO</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" customFormat="1" s="2">
-      <c r="A14" s="7" t="n"/>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>Rector Summary</t>
-        </is>
-      </c>
-      <c r="C14" s="10" t="inlineStr">
-        <is>
-          <t>E-mail</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>Once per semester</t>
-        </is>
-      </c>
-      <c r="E14" s="9" t="inlineStr">
-        <is>
-          <t>Report status, pilot results and the scaling decision needed</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="inlineStr">
-        <is>
-          <t>Project Manager</t>
-        </is>
-      </c>
-      <c r="G14" s="9" t="inlineStr">
-        <is>
-          <t>N. Shakhovska (Rector), PM</t>
+      <c r="D14" s="19" t="inlineStr">
+        <is>
+          <t>Every two weeks, Friday</t>
+        </is>
+      </c>
+      <c r="E14" s="21" t="inlineStr">
+        <is>
+          <t>Identify what works and what does not, and agree concrete process improvements for the next two weeks</t>
+        </is>
+      </c>
+      <c r="F14" s="19" t="inlineStr">
+        <is>
+          <t>Project Manager (N. Zankovych)</t>
+        </is>
+      </c>
+      <c r="G14" s="21" t="inlineStr">
+        <is>
+          <t>Whole project team</t>
         </is>
       </c>
       <c r="H14" s="1" t="n"/>
@@ -1818,23 +1833,312 @@
       <c r="JY14" s="1" t="n"/>
       <c r="JZ14" s="1" t="n"/>
     </row>
-    <row r="15" customFormat="1" s="1"/>
-    <row r="16" customFormat="1" s="1"/>
+    <row r="15" ht="42" customFormat="1" customHeight="1" s="1">
+      <c r="B15" s="19" t="inlineStr">
+        <is>
+          <t>Change Management Meeting</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>Meeting</t>
+        </is>
+      </c>
+      <c r="D15" s="19" t="inlineStr">
+        <is>
+          <t>As needed, within 2 business days of a request</t>
+        </is>
+      </c>
+      <c r="E15" s="21" t="inlineStr">
+        <is>
+          <t>Review a scope change request, assess the impact on the schedule and take a decision</t>
+        </is>
+      </c>
+      <c r="F15" s="19" t="inlineStr">
+        <is>
+          <t>Product Owner (K. Holovskyi)</t>
+        </is>
+      </c>
+      <c r="G15" s="21" t="inlineStr">
+        <is>
+          <t>PO, PM, BA, Tech Lead; the sponsor for material changes</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="56" customFormat="1" customHeight="1" s="1">
+      <c r="B16" s="19" t="inlineStr">
+        <is>
+          <t>Semester Report to the Ministry of Education and Science</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>Official one-page report</t>
+        </is>
+      </c>
+      <c r="D16" s="19" t="inlineStr">
+        <is>
+          <t>Once per semester and at control points</t>
+        </is>
+      </c>
+      <c r="E16" s="21" t="inlineStr">
+        <is>
+          <t>Keep the regulator satisfied: report progress, pilot results and compliance with personal-data and educational IT regulation</t>
+        </is>
+      </c>
+      <c r="F16" s="19" t="inlineStr">
+        <is>
+          <t>Project Manager (N. Zankovych)</t>
+        </is>
+      </c>
+      <c r="G16" s="21" t="inlineStr">
+        <is>
+          <t>Ministry of Education and Science of Ukraine, Lviv Polytechnic National University, PM</t>
+        </is>
+      </c>
+    </row>
     <row r="17" customFormat="1" s="1"/>
-    <row r="18" customFormat="1" s="1"/>
-    <row r="19" customFormat="1" s="1"/>
-    <row r="20" customFormat="1" s="1"/>
-    <row r="21" customFormat="1" s="1"/>
-    <row r="22" customFormat="1" s="1"/>
-    <row r="23" customFormat="1" s="1"/>
+    <row r="18" customFormat="1" s="1">
+      <c r="B18" s="16" t="inlineStr">
+        <is>
+          <t>COMMUNICATION ESCALATION PROCESS</t>
+        </is>
+      </c>
+      <c r="C18" s="18" t="n"/>
+      <c r="D18" s="18" t="n"/>
+      <c r="E18" s="18" t="n"/>
+      <c r="F18" s="18" t="n"/>
+      <c r="G18" s="18" t="n"/>
+    </row>
+    <row r="19" ht="18" customFormat="1" customHeight="1" s="1">
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D19" s="22" t="n"/>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>Decision Authority</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>Timeframe for Resolution</t>
+        </is>
+      </c>
+      <c r="G19" s="22" t="n"/>
+    </row>
+    <row r="20" ht="32" customFormat="1" customHeight="1" s="1">
+      <c r="B20" s="19" t="inlineStr">
+        <is>
+          <t>Priority 1</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>Major impact: the team is blocked, or the pilot or project deadline is at risk</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="n"/>
+      <c r="E20" s="21" t="inlineStr">
+        <is>
+          <t>Lviv Polytechnic National University (Sponsor)</t>
+        </is>
+      </c>
+      <c r="F20" s="19" t="inlineStr">
+        <is>
+          <t>Within 1 business day</t>
+        </is>
+      </c>
+      <c r="G20" s="22" t="n"/>
+    </row>
+    <row r="21" ht="32" customFormat="1" customHeight="1" s="1">
+      <c r="B21" s="19" t="inlineStr">
+        <is>
+          <t>Priority 2</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>Medium impact: individual activities or the MVP scope may slip</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="n"/>
+      <c r="E21" s="21" t="inlineStr">
+        <is>
+          <t>Product Owner</t>
+        </is>
+      </c>
+      <c r="F21" s="19" t="inlineStr">
+        <is>
+          <t>Within 2 business days</t>
+        </is>
+      </c>
+      <c r="G21" s="22" t="n"/>
+    </row>
+    <row r="22" ht="32" customFormat="1" customHeight="1" s="1">
+      <c r="B22" s="19" t="inlineStr">
+        <is>
+          <t>Priority 3</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>Slight impact: minor scheduling difficulties with no effect on scope or outcome</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="n"/>
+      <c r="E22" s="21" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="F22" s="19" t="inlineStr">
+        <is>
+          <t>Within 3 business days</t>
+        </is>
+      </c>
+      <c r="G22" s="22" t="n"/>
+    </row>
+    <row r="23" ht="32" customFormat="1" customHeight="1" s="1">
+      <c r="B23" s="19" t="inlineStr">
+        <is>
+          <t>Priority 4</t>
+        </is>
+      </c>
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>No impact on the project, but a better solution may exist</t>
+        </is>
+      </c>
+      <c r="D23" s="22" t="n"/>
+      <c r="E23" s="21" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="F23" s="19" t="inlineStr">
+        <is>
+          <t>Handled through the change management process</t>
+        </is>
+      </c>
+      <c r="G23" s="22" t="n"/>
+    </row>
     <row r="24" customFormat="1" s="1"/>
-    <row r="25" customFormat="1" s="1"/>
-    <row r="26" customFormat="1" s="1"/>
-    <row r="27" customFormat="1" s="1"/>
-    <row r="28" customFormat="1" s="1"/>
-    <row r="29" customFormat="1" s="1"/>
-    <row r="30" customFormat="1" s="1"/>
-    <row r="31" customFormat="1" s="1"/>
+    <row r="25" customFormat="1" s="1">
+      <c r="B25" s="16" t="inlineStr">
+        <is>
+          <t>COMMUNICATION STANDARDS</t>
+        </is>
+      </c>
+      <c r="C25" s="18" t="n"/>
+      <c r="D25" s="18" t="n"/>
+      <c r="E25" s="18" t="n"/>
+      <c r="F25" s="18" t="n"/>
+      <c r="G25" s="18" t="n"/>
+    </row>
+    <row r="26" ht="36" customFormat="1" customHeight="1" s="1">
+      <c r="B26" s="19" t="inlineStr">
+        <is>
+          <t>Meeting agenda</t>
+        </is>
+      </c>
+      <c r="C26" s="20" t="inlineStr">
+        <is>
+          <t>Distributed to participants no later than 2 business days before the meeting; identifies the topics, the presenter and a time limit for each. The first item is always a review of action items from the previous meeting.</t>
+        </is>
+      </c>
+      <c r="D26" s="23" t="n"/>
+      <c r="E26" s="23" t="n"/>
+      <c r="F26" s="23" t="n"/>
+      <c r="G26" s="22" t="n"/>
+    </row>
+    <row r="27" ht="36" customFormat="1" customHeight="1" s="1">
+      <c r="B27" s="19" t="inlineStr">
+        <is>
+          <t>Meeting minutes</t>
+        </is>
+      </c>
+      <c r="C27" s="20" t="inlineStr">
+        <is>
+          <t>Published within 1 business day after the meeting; contain the decisions taken, new action items with a named owner and due date, and the Parking Lot list.</t>
+        </is>
+      </c>
+      <c r="D27" s="23" t="n"/>
+      <c r="E27" s="23" t="n"/>
+      <c r="F27" s="23" t="n"/>
+      <c r="G27" s="22" t="n"/>
+    </row>
+    <row r="28" ht="36" customFormat="1" customHeight="1" s="1">
+      <c r="B28" s="19" t="inlineStr">
+        <is>
+          <t>Channels</t>
+        </is>
+      </c>
+      <c r="C28" s="20" t="inlineStr">
+        <is>
+          <t>Formal documents and approvals — university @lpnu.ua mailboxes. Day-to-day team work — team chat. Tasks and defects — issue tracker.</t>
+        </is>
+      </c>
+      <c r="D28" s="23" t="n"/>
+      <c r="E28" s="23" t="n"/>
+      <c r="F28" s="23" t="n"/>
+      <c r="G28" s="22" t="n"/>
+    </row>
+    <row r="29" ht="36" customFormat="1" customHeight="1" s="1">
+      <c r="B29" s="19" t="inlineStr">
+        <is>
+          <t>Confidentiality</t>
+        </is>
+      </c>
+      <c r="C29" s="20" t="inlineStr">
+        <is>
+          <t>Personal data of students and lecturers is not distributed through external channels. Any transfer of course materials to the external LLM API is approved by Lviv Polytechnic National University as the owner of the data.</t>
+        </is>
+      </c>
+      <c r="D29" s="23" t="n"/>
+      <c r="E29" s="23" t="n"/>
+      <c r="F29" s="23" t="n"/>
+      <c r="G29" s="22" t="n"/>
+    </row>
+    <row r="30" ht="36" customFormat="1" customHeight="1" s="1">
+      <c r="B30" s="19" t="inlineStr">
+        <is>
+          <t>Escalation rule</t>
+        </is>
+      </c>
+      <c r="C30" s="20" t="inlineStr">
+        <is>
+          <t>Issues involving personal data or the transfer of materials to the external LLM API are escalated to the sponsor regardless of the priority assigned.</t>
+        </is>
+      </c>
+      <c r="D30" s="23" t="n"/>
+      <c r="E30" s="23" t="n"/>
+      <c r="F30" s="23" t="n"/>
+      <c r="G30" s="22" t="n"/>
+    </row>
+    <row r="31" ht="36" customFormat="1" customHeight="1" s="1">
+      <c r="B31" s="19" t="inlineStr">
+        <is>
+          <t>Link to the register</t>
+        </is>
+      </c>
+      <c r="C31" s="20" t="inlineStr">
+        <is>
+          <t>The frequency and method of each communication match the “Preferable way of communication” and “Frequency of Communication” columns in “1. Stakeholder Register_VNS.xlsx”.</t>
+        </is>
+      </c>
+      <c r="D31" s="23" t="n"/>
+      <c r="E31" s="23" t="n"/>
+      <c r="F31" s="23" t="n"/>
+      <c r="G31" s="22" t="n"/>
+    </row>
     <row r="32" customFormat="1" s="1"/>
     <row r="33" customFormat="1" s="1"/>
     <row r="34" customFormat="1" s="1"/>
@@ -1854,8 +2158,26 @@
     <row r="48" customFormat="1" s="1"/>
     <row r="49" customFormat="1" s="1"/>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="19">
     <mergeCell ref="B2:G2"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="B25:G25"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="B18:G18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>

--- a/BA/Part 1_Stakeholder Analysis amp Management-20260912/Done/Manual/Artifacts/4. Communication Plan_VNS.xlsx
+++ b/BA/Part 1_Stakeholder Analysis amp Management-20260912/Done/Manual/Artifacts/4. Communication Plan_VNS.xlsx
@@ -606,7 +606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:JZ31"/>
+  <dimension ref="A2:JZ60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="8.875" customWidth="1" style="1" min="1" max="1"/>
@@ -1898,247 +1898,20 @@
       </c>
     </row>
     <row r="17" customFormat="1" s="1"/>
-    <row r="18" customFormat="1" s="1">
-      <c r="B18" s="16" t="inlineStr">
-        <is>
-          <t>COMMUNICATION ESCALATION PROCESS</t>
-        </is>
-      </c>
-      <c r="C18" s="18" t="n"/>
-      <c r="D18" s="18" t="n"/>
-      <c r="E18" s="18" t="n"/>
-      <c r="F18" s="18" t="n"/>
-      <c r="G18" s="18" t="n"/>
-    </row>
-    <row r="19" ht="18" customFormat="1" customHeight="1" s="1">
-      <c r="B19" s="11" t="inlineStr">
-        <is>
-          <t>Priority</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>Definition</t>
-        </is>
-      </c>
-      <c r="D19" s="22" t="n"/>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>Decision Authority</t>
-        </is>
-      </c>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <t>Timeframe for Resolution</t>
-        </is>
-      </c>
-      <c r="G19" s="22" t="n"/>
-    </row>
-    <row r="20" ht="32" customFormat="1" customHeight="1" s="1">
-      <c r="B20" s="19" t="inlineStr">
-        <is>
-          <t>Priority 1</t>
-        </is>
-      </c>
-      <c r="C20" s="20" t="inlineStr">
-        <is>
-          <t>Major impact: the team is blocked, or the pilot or project deadline is at risk</t>
-        </is>
-      </c>
-      <c r="D20" s="22" t="n"/>
-      <c r="E20" s="21" t="inlineStr">
-        <is>
-          <t>Lviv Polytechnic National University (Sponsor)</t>
-        </is>
-      </c>
-      <c r="F20" s="19" t="inlineStr">
-        <is>
-          <t>Within 1 business day</t>
-        </is>
-      </c>
-      <c r="G20" s="22" t="n"/>
-    </row>
-    <row r="21" ht="32" customFormat="1" customHeight="1" s="1">
-      <c r="B21" s="19" t="inlineStr">
-        <is>
-          <t>Priority 2</t>
-        </is>
-      </c>
-      <c r="C21" s="20" t="inlineStr">
-        <is>
-          <t>Medium impact: individual activities or the MVP scope may slip</t>
-        </is>
-      </c>
-      <c r="D21" s="22" t="n"/>
-      <c r="E21" s="21" t="inlineStr">
-        <is>
-          <t>Product Owner</t>
-        </is>
-      </c>
-      <c r="F21" s="19" t="inlineStr">
-        <is>
-          <t>Within 2 business days</t>
-        </is>
-      </c>
-      <c r="G21" s="22" t="n"/>
-    </row>
-    <row r="22" ht="32" customFormat="1" customHeight="1" s="1">
-      <c r="B22" s="19" t="inlineStr">
-        <is>
-          <t>Priority 3</t>
-        </is>
-      </c>
-      <c r="C22" s="20" t="inlineStr">
-        <is>
-          <t>Slight impact: minor scheduling difficulties with no effect on scope or outcome</t>
-        </is>
-      </c>
-      <c r="D22" s="22" t="n"/>
-      <c r="E22" s="21" t="inlineStr">
-        <is>
-          <t>Project Manager</t>
-        </is>
-      </c>
-      <c r="F22" s="19" t="inlineStr">
-        <is>
-          <t>Within 3 business days</t>
-        </is>
-      </c>
-      <c r="G22" s="22" t="n"/>
-    </row>
-    <row r="23" ht="32" customFormat="1" customHeight="1" s="1">
-      <c r="B23" s="19" t="inlineStr">
-        <is>
-          <t>Priority 4</t>
-        </is>
-      </c>
-      <c r="C23" s="20" t="inlineStr">
-        <is>
-          <t>No impact on the project, but a better solution may exist</t>
-        </is>
-      </c>
-      <c r="D23" s="22" t="n"/>
-      <c r="E23" s="21" t="inlineStr">
-        <is>
-          <t>Project Manager</t>
-        </is>
-      </c>
-      <c r="F23" s="19" t="inlineStr">
-        <is>
-          <t>Handled through the change management process</t>
-        </is>
-      </c>
-      <c r="G23" s="22" t="n"/>
-    </row>
+    <row r="18" customFormat="1" s="1"/>
+    <row r="19" customFormat="1" s="1"/>
+    <row r="20" customFormat="1" s="1"/>
+    <row r="21" customFormat="1" s="1"/>
+    <row r="22" customFormat="1" s="1"/>
+    <row r="23" customFormat="1" s="1"/>
     <row r="24" customFormat="1" s="1"/>
-    <row r="25" customFormat="1" s="1">
-      <c r="B25" s="16" t="inlineStr">
-        <is>
-          <t>COMMUNICATION STANDARDS</t>
-        </is>
-      </c>
-      <c r="C25" s="18" t="n"/>
-      <c r="D25" s="18" t="n"/>
-      <c r="E25" s="18" t="n"/>
-      <c r="F25" s="18" t="n"/>
-      <c r="G25" s="18" t="n"/>
-    </row>
-    <row r="26" ht="36" customFormat="1" customHeight="1" s="1">
-      <c r="B26" s="19" t="inlineStr">
-        <is>
-          <t>Meeting agenda</t>
-        </is>
-      </c>
-      <c r="C26" s="20" t="inlineStr">
-        <is>
-          <t>Distributed to participants no later than 2 business days before the meeting; identifies the topics, the presenter and a time limit for each. The first item is always a review of action items from the previous meeting.</t>
-        </is>
-      </c>
-      <c r="D26" s="23" t="n"/>
-      <c r="E26" s="23" t="n"/>
-      <c r="F26" s="23" t="n"/>
-      <c r="G26" s="22" t="n"/>
-    </row>
-    <row r="27" ht="36" customFormat="1" customHeight="1" s="1">
-      <c r="B27" s="19" t="inlineStr">
-        <is>
-          <t>Meeting minutes</t>
-        </is>
-      </c>
-      <c r="C27" s="20" t="inlineStr">
-        <is>
-          <t>Published within 1 business day after the meeting; contain the decisions taken, new action items with a named owner and due date, and the Parking Lot list.</t>
-        </is>
-      </c>
-      <c r="D27" s="23" t="n"/>
-      <c r="E27" s="23" t="n"/>
-      <c r="F27" s="23" t="n"/>
-      <c r="G27" s="22" t="n"/>
-    </row>
-    <row r="28" ht="36" customFormat="1" customHeight="1" s="1">
-      <c r="B28" s="19" t="inlineStr">
-        <is>
-          <t>Channels</t>
-        </is>
-      </c>
-      <c r="C28" s="20" t="inlineStr">
-        <is>
-          <t>Formal documents and approvals — university @lpnu.ua mailboxes. Day-to-day team work — team chat. Tasks and defects — issue tracker.</t>
-        </is>
-      </c>
-      <c r="D28" s="23" t="n"/>
-      <c r="E28" s="23" t="n"/>
-      <c r="F28" s="23" t="n"/>
-      <c r="G28" s="22" t="n"/>
-    </row>
-    <row r="29" ht="36" customFormat="1" customHeight="1" s="1">
-      <c r="B29" s="19" t="inlineStr">
-        <is>
-          <t>Confidentiality</t>
-        </is>
-      </c>
-      <c r="C29" s="20" t="inlineStr">
-        <is>
-          <t>Personal data of students and lecturers is not distributed through external channels. Any transfer of course materials to the external LLM API is approved by Lviv Polytechnic National University as the owner of the data.</t>
-        </is>
-      </c>
-      <c r="D29" s="23" t="n"/>
-      <c r="E29" s="23" t="n"/>
-      <c r="F29" s="23" t="n"/>
-      <c r="G29" s="22" t="n"/>
-    </row>
-    <row r="30" ht="36" customFormat="1" customHeight="1" s="1">
-      <c r="B30" s="19" t="inlineStr">
-        <is>
-          <t>Escalation rule</t>
-        </is>
-      </c>
-      <c r="C30" s="20" t="inlineStr">
-        <is>
-          <t>Issues involving personal data or the transfer of materials to the external LLM API are escalated to the sponsor regardless of the priority assigned.</t>
-        </is>
-      </c>
-      <c r="D30" s="23" t="n"/>
-      <c r="E30" s="23" t="n"/>
-      <c r="F30" s="23" t="n"/>
-      <c r="G30" s="22" t="n"/>
-    </row>
-    <row r="31" ht="36" customFormat="1" customHeight="1" s="1">
-      <c r="B31" s="19" t="inlineStr">
-        <is>
-          <t>Link to the register</t>
-        </is>
-      </c>
-      <c r="C31" s="20" t="inlineStr">
-        <is>
-          <t>The frequency and method of each communication match the “Preferable way of communication” and “Frequency of Communication” columns in “1. Stakeholder Register_VNS.xlsx”.</t>
-        </is>
-      </c>
-      <c r="D31" s="23" t="n"/>
-      <c r="E31" s="23" t="n"/>
-      <c r="F31" s="23" t="n"/>
-      <c r="G31" s="22" t="n"/>
-    </row>
+    <row r="25" customFormat="1" s="1"/>
+    <row r="26" customFormat="1" s="1"/>
+    <row r="27" customFormat="1" s="1"/>
+    <row r="28" customFormat="1" s="1"/>
+    <row r="29" customFormat="1" s="1"/>
+    <row r="30" customFormat="1" s="1"/>
+    <row r="31" customFormat="1" s="1"/>
     <row r="32" customFormat="1" s="1"/>
     <row r="33" customFormat="1" s="1"/>
     <row r="34" customFormat="1" s="1"/>
@@ -2157,27 +1930,20 @@
     <row r="47" customFormat="1" s="1"/>
     <row r="48" customFormat="1" s="1"/>
     <row r="49" customFormat="1" s="1"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
+    <row r="60"/>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="1">
     <mergeCell ref="B2:G2"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C29:G29"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C31:G31"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="C27:G27"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="B25:G25"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="B18:G18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
